--- a/sampledata/Assement-Format-Category A-Stage 1-Family (2).xlsx
+++ b/sampledata/Assement-Format-Category A-Stage 1-Family (2).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\RLLT\Webapp\sampledata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BEF94FF-C896-4984-BD02-81F83E7AA06B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{364602A9-5D64-47D7-9634-F8727B3D766F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="33">
   <si>
     <r>
       <rPr>
@@ -393,6 +393,12 @@
       </rPr>
       <t>me.</t>
     </r>
+  </si>
+  <si>
+    <t>Choice 4</t>
+  </si>
+  <si>
+    <t>Choice 5</t>
   </si>
 </sst>
 </file>
@@ -548,26 +554,41 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="7"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
@@ -576,12 +597,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -599,17 +614,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="7"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -915,7 +921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.33203125" customWidth="1"/>
@@ -927,10 +933,12 @@
     <col min="9" max="9" width="18.6640625" customWidth="1"/>
     <col min="10" max="10" width="12.6640625" customWidth="1"/>
     <col min="11" max="11" width="19.77734375" customWidth="1"/>
-    <col min="12" max="13" width="12.6640625" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" customWidth="1"/>
+    <col min="13" max="13" width="19" customWidth="1"/>
+    <col min="15" max="15" width="19.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -946,10 +954,10 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="18"/>
+      <c r="G1" s="23"/>
       <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
@@ -965,9 +973,20 @@
       <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="5"/>
+      <c r="M1" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:13" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -983,10 +1002,10 @@
       <c r="E2" s="6">
         <v>1</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="20"/>
+      <c r="G2" s="17"/>
       <c r="H2" s="6">
         <v>5</v>
       </c>
@@ -1002,10 +1021,21 @@
       <c r="L2" s="6">
         <v>1</v>
       </c>
-      <c r="M2" s="10"/>
+      <c r="M2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="6">
+        <v>1</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="6">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:13" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11">
+    <row r="3" spans="1:16" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="10">
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
@@ -1017,31 +1047,42 @@
       <c r="D3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="11">
-        <v>1</v>
-      </c>
-      <c r="F3" s="21" t="s">
+      <c r="E3" s="10">
+        <v>1</v>
+      </c>
+      <c r="F3" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="22"/>
-      <c r="H3" s="11">
+      <c r="G3" s="25"/>
+      <c r="H3" s="10">
         <v>3</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="11">
+      <c r="J3" s="10">
         <v>5</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="11">
-        <v>1</v>
-      </c>
-      <c r="M3" s="10"/>
+      <c r="L3" s="10">
+        <v>1</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" s="10">
+        <v>1</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="P3" s="10">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>3</v>
       </c>
@@ -1057,32 +1098,43 @@
       <c r="E4" s="6">
         <v>1</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="24"/>
+      <c r="G4" s="27"/>
       <c r="H4" s="6">
         <v>3</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="13" t="s">
         <v>21</v>
       </c>
       <c r="J4" s="6">
         <v>1</v>
       </c>
-      <c r="K4" s="14" t="s">
+      <c r="K4" s="13" t="s">
         <v>22</v>
       </c>
       <c r="L4" s="6">
         <v>5</v>
       </c>
-      <c r="M4" s="10"/>
+      <c r="M4" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="N4" s="6">
+        <v>5</v>
+      </c>
+      <c r="O4" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="P4" s="6">
+        <v>5</v>
+      </c>
     </row>
-    <row r="5" spans="1:13" ht="64.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="64.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>4</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -1094,14 +1146,14 @@
       <c r="E5" s="6">
         <v>1</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="F5" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="26"/>
+      <c r="G5" s="29"/>
       <c r="H5" s="6">
         <v>5</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="11" t="s">
         <v>25</v>
       </c>
       <c r="J5" s="6">
@@ -1113,9 +1165,20 @@
       <c r="L5" s="6">
         <v>1</v>
       </c>
-      <c r="M5" s="10"/>
+      <c r="M5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" s="6">
+        <v>1</v>
+      </c>
+      <c r="O5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="P5" s="6">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:13" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" ht="97.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>5</v>
       </c>
@@ -1131,10 +1194,10 @@
       <c r="E6" s="6">
         <v>1</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="20"/>
+      <c r="G6" s="17"/>
       <c r="H6" s="6">
         <v>5</v>
       </c>
@@ -1144,87 +1207,98 @@
       <c r="J6" s="6">
         <v>1</v>
       </c>
-      <c r="K6" s="13" t="s">
+      <c r="K6" s="12" t="s">
         <v>30</v>
       </c>
       <c r="L6" s="6">
         <v>3</v>
       </c>
-      <c r="M6" s="10"/>
+      <c r="M6" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="N6" s="6">
+        <v>3</v>
+      </c>
+      <c r="O6" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="P6" s="6">
+        <v>3</v>
+      </c>
     </row>
-    <row r="7" spans="1:13" ht="13.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="16"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
+    <row r="7" spans="1:16" ht="13.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
       <c r="M7" s="5"/>
     </row>
-    <row r="8" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="16"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
+    <row r="8" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
       <c r="M8" s="5"/>
     </row>
-    <row r="9" spans="1:13" ht="67.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="29"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
+    <row r="9" spans="1:16" ht="67.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="20"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
     </row>
-    <row r="10" spans="1:13" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="29"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="30"/>
-      <c r="K10" s="30"/>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
+    <row r="10" spans="1:16" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F5:G5"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="A9:M9"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="G10:M10"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
